--- a/artfynd/S 971-2023 artfynd.xlsx
+++ b/artfynd/S 971-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AZ30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -785,6 +790,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113191184</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69614410</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1003,6 +1018,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96336066</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1108,6 +1128,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96336249</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1233,6 +1258,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69614432</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1338,6 +1368,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73112944</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1451,6 +1486,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73121229</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1552,6 +1592,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103511669</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1657,6 +1702,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104198259</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1758,6 +1808,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103511844</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1871,6 +1926,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104198248</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1987,6 +2047,11 @@
       <c r="AY13" t="inlineStr">
         <is>
           <t>Ansvarsarter i Norrtälje kommun</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98668974</t>
         </is>
       </c>
     </row>
@@ -2094,6 +2159,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96336071</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2199,6 +2269,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69614389</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2304,6 +2379,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69614390</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2413,6 +2493,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73112931</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2523,6 +2608,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104198289</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2624,6 +2714,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104185452</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2723,6 +2818,11 @@
       <c r="AY20" t="inlineStr">
         <is>
           <t>Stora Obrutna Skogsområden</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106521488</t>
         </is>
       </c>
     </row>
@@ -2830,6 +2930,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96336286</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2930,6 +3035,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73121176</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3042,6 +3152,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134479398</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3168,6 +3283,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132982745</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3289,6 +3409,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134479438</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3405,6 +3530,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133491851</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3506,6 +3636,11 @@
           <t>Stora Obrutna Skogsområden</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106521486</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3607,6 +3742,11 @@
           <t>Stora Obrutna Skogsområden</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106521490</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3719,6 +3859,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133491530</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3835,8 +3980,44 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109010924</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>